--- a/Task1/drafts/results/validation_deltas.xlsx
+++ b/Task1/drafts/results/validation_deltas.xlsx
@@ -478,31 +478,31 @@
         <v>45748</v>
       </c>
       <c r="B2" t="n">
-        <v>-9.999228432050607</v>
+        <v>-0.9369229002685664</v>
       </c>
       <c r="C2" t="n">
-        <v>-9.232784158876992</v>
+        <v>-1.391904637841218</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.571715585350589</v>
+        <v>-1.410119843166541</v>
       </c>
       <c r="E2" t="n">
-        <v>-10.08310317528257</v>
+        <v>-1.971763085761232</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.4367940928898</v>
+        <v>-1.028012516041464</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.07310364216077</v>
+        <v>-2.505557312819249</v>
       </c>
       <c r="H2" t="n">
-        <v>-13.06756663099463</v>
+        <v>-3.558786472824082</v>
       </c>
       <c r="I2" t="n">
-        <v>-13.16486291889957</v>
+        <v>-2.691506127621537</v>
       </c>
       <c r="J2" t="n">
-        <v>-19.41709514564408</v>
+        <v>-3.241090382538459</v>
       </c>
     </row>
     <row r="3">
@@ -510,31 +510,31 @@
         <v>45778</v>
       </c>
       <c r="B3" t="n">
-        <v>-10.05019243157887</v>
+        <v>-1.662651406145372</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.7344180715289</v>
+        <v>-2.678530063224333</v>
       </c>
       <c r="D3" t="n">
-        <v>-11.07465979900978</v>
+        <v>-2.419568661270031</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.20030065632119</v>
+        <v>-2.721388398057364</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.904464188686703</v>
+        <v>-2.046245646128526</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.673209519112827</v>
+        <v>-2.619484773353172</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.50783979272336</v>
+        <v>-3.191152319911581</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.297222521940014</v>
+        <v>-0.5216008369050442</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8302490627324914</v>
+        <v>-1.414804096196335</v>
       </c>
     </row>
     <row r="4">
@@ -542,31 +542,31 @@
         <v>45809</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.314737403188371</v>
+        <v>-1.120186354614209</v>
       </c>
       <c r="C4" t="n">
-        <v>-3.166698944503157</v>
+        <v>-1.869028565667413</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.983533348525331</v>
+        <v>-1.27567040234474</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.115570697068218</v>
+        <v>-1.863641073498691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3413642024366439</v>
+        <v>-1.026196749163404</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9462859821303979</v>
+        <v>-0.8560390388473778</v>
       </c>
       <c r="H4" t="n">
-        <v>3.475744503345254</v>
+        <v>-2.536366096099144</v>
       </c>
       <c r="I4" t="n">
-        <v>7.293723900466873</v>
+        <v>2.168796933495486</v>
       </c>
       <c r="J4" t="n">
-        <v>18.11041572859143</v>
+        <v>3.370686534383594</v>
       </c>
     </row>
     <row r="5">
@@ -574,31 +574,31 @@
         <v>45839</v>
       </c>
       <c r="B5" t="n">
-        <v>3.835536311029578</v>
+        <v>-0.07785047413025836</v>
       </c>
       <c r="C5" t="n">
-        <v>4.16836911988625</v>
+        <v>-0.4991933007692921</v>
       </c>
       <c r="D5" t="n">
-        <v>4.760743752997993</v>
+        <v>0.09002234579124391</v>
       </c>
       <c r="E5" t="n">
-        <v>5.559053160156399</v>
+        <v>0.2996159236847014</v>
       </c>
       <c r="F5" t="n">
-        <v>6.739763553309409</v>
+        <v>1.381641536623896</v>
       </c>
       <c r="G5" t="n">
-        <v>8.141529249292425</v>
+        <v>2.748005311659078</v>
       </c>
       <c r="H5" t="n">
-        <v>11.53586126960767</v>
+        <v>0.8494079767773641</v>
       </c>
       <c r="I5" t="n">
-        <v>16.14626567498983</v>
+        <v>7.285237545852375</v>
       </c>
       <c r="J5" t="n">
-        <v>25.5900387071293</v>
+        <v>8.274569290962532</v>
       </c>
     </row>
     <row r="6">
@@ -606,31 +606,31 @@
         <v>45870</v>
       </c>
       <c r="B6" t="n">
-        <v>5.271845421086248</v>
+        <v>2.818386593933177</v>
       </c>
       <c r="C6" t="n">
-        <v>5.091886282522214</v>
+        <v>2.189844031594969</v>
       </c>
       <c r="D6" t="n">
-        <v>5.901262275753112</v>
+        <v>1.837705608613255</v>
       </c>
       <c r="E6" t="n">
-        <v>5.784768469998596</v>
+        <v>3.216713496292229</v>
       </c>
       <c r="F6" t="n">
-        <v>6.866618723713774</v>
+        <v>3.476203494448992</v>
       </c>
       <c r="G6" t="n">
-        <v>7.97358580733389</v>
+        <v>6.878252835655815</v>
       </c>
       <c r="H6" t="n">
-        <v>12.05539162404339</v>
+        <v>4.049994444980804</v>
       </c>
       <c r="I6" t="n">
-        <v>18.28131072717426</v>
+        <v>12.88417111781342</v>
       </c>
       <c r="J6" t="n">
-        <v>21.17462992827826</v>
+        <v>13.31113027877863</v>
       </c>
     </row>
     <row r="7">
@@ -638,31 +638,31 @@
         <v>45901</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1778428477032357</v>
+        <v>4.045786251088121</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3395475368999712</v>
+        <v>3.167832838113675</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02960167412825854</v>
+        <v>3.047604372466679</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2767815878820166</v>
+        <v>4.583723527248889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002855289502612379</v>
+        <v>4.141440107083103</v>
       </c>
       <c r="G7" t="n">
-        <v>0.320647372084629</v>
+        <v>7.656862034465981</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6401426357275</v>
+        <v>4.825351393393134</v>
       </c>
       <c r="I7" t="n">
-        <v>5.547725123695187</v>
+        <v>12.65250258818565</v>
       </c>
       <c r="J7" t="n">
-        <v>7.253736680745448</v>
+        <v>13.76143448543108</v>
       </c>
     </row>
   </sheetData>
@@ -736,31 +736,31 @@
         <v>45748</v>
       </c>
       <c r="B2" t="n">
-        <v>-7.407481551301206</v>
+        <v>-1.177028621947983</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.790044318077491</v>
+        <v>-0.8930810352195202</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.159635818421535</v>
+        <v>-1.121784985949176</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.510596985549878</v>
+        <v>-2.079773493255107</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.481562558805521</v>
+        <v>-0.8562040934137372</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.139493755529845</v>
+        <v>-3.692286758484926</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.942872075663317</v>
+        <v>-4.055852571762152</v>
       </c>
       <c r="I2" t="n">
-        <v>-9.831251592834825</v>
+        <v>-2.366615332047282</v>
       </c>
       <c r="J2" t="n">
-        <v>-14.73829619982074</v>
+        <v>-2.320343594129156</v>
       </c>
     </row>
     <row r="3">
@@ -768,31 +768,31 @@
         <v>45778</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.365927684119772</v>
+        <v>-1.479272707501703</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.986720819653666</v>
+        <v>-2.086766606740223</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.263593597661981</v>
+        <v>-1.20264732717003</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.318101344616736</v>
+        <v>-2.652623992562646</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.266302248622239</v>
+        <v>-1.867292785650733</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.107079649776271</v>
+        <v>-5.520659561926109</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.197414737441001</v>
+        <v>-4.751177790301291</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.261167205848707</v>
+        <v>0.7935417527163864</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6796490337949876</v>
+        <v>0.9446210412678084</v>
       </c>
     </row>
     <row r="4">
@@ -800,31 +800,31 @@
         <v>45809</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.365166772317611</v>
+        <v>-0.9042156193110102</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.079363902528048</v>
+        <v>-1.249659721445575</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.162094897760344</v>
+        <v>0.7531078235177624</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.289258431660016</v>
+        <v>-2.064494674555903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6430497030574429</v>
+        <v>-0.3561406080231393</v>
       </c>
       <c r="G4" t="n">
-        <v>1.178184056726799</v>
+        <v>-5.344120169480831</v>
       </c>
       <c r="H4" t="n">
-        <v>3.043529247797323</v>
+        <v>-4.240133500425351</v>
       </c>
       <c r="I4" t="n">
-        <v>6.29970966627323</v>
+        <v>3.514432344955324</v>
       </c>
       <c r="J4" t="n">
-        <v>14.2057906729036</v>
+        <v>6.286840421789321</v>
       </c>
     </row>
     <row r="5">
@@ -832,31 +832,31 @@
         <v>45839</v>
       </c>
       <c r="B5" t="n">
-        <v>3.650464349556195</v>
+        <v>0.08224139303235489</v>
       </c>
       <c r="C5" t="n">
-        <v>3.826481536682635</v>
+        <v>0.1099022826946481</v>
       </c>
       <c r="D5" t="n">
-        <v>4.760743752997993</v>
+        <v>3.064622125195196</v>
       </c>
       <c r="E5" t="n">
-        <v>5.262296861379088</v>
+        <v>-0.5214331675610993</v>
       </c>
       <c r="F5" t="n">
-        <v>6.739763553309409</v>
+        <v>2.550280960827848</v>
       </c>
       <c r="G5" t="n">
-        <v>8.141529249292425</v>
+        <v>-2.818250735008959</v>
       </c>
       <c r="H5" t="n">
-        <v>10.81507980379997</v>
+        <v>-0.7734530574600882</v>
       </c>
       <c r="I5" t="n">
-        <v>15.93927814698164</v>
+        <v>7.805722348530104</v>
       </c>
       <c r="J5" t="n">
-        <v>20.53962324701445</v>
+        <v>12.85574076924262</v>
       </c>
     </row>
     <row r="6">
@@ -864,31 +864,31 @@
         <v>45870</v>
       </c>
       <c r="B6" t="n">
-        <v>4.896233135669775</v>
+        <v>2.327000486496317</v>
       </c>
       <c r="C6" t="n">
-        <v>4.717723019386934</v>
+        <v>2.905943674438038</v>
       </c>
       <c r="D6" t="n">
-        <v>5.360600812536752</v>
+        <v>5.142960403734612</v>
       </c>
       <c r="E6" t="n">
-        <v>5.210572110383488</v>
+        <v>3.549138537274409</v>
       </c>
       <c r="F6" t="n">
-        <v>6.238110299716045</v>
+        <v>7.30370806778399</v>
       </c>
       <c r="G6" t="n">
-        <v>7.236241297957143</v>
+        <v>-0.8847515044015992</v>
       </c>
       <c r="H6" t="n">
-        <v>10.60916605624015</v>
+        <v>2.487640941680155</v>
       </c>
       <c r="I6" t="n">
-        <v>16.04140231762937</v>
+        <v>14.38593156287409</v>
       </c>
       <c r="J6" t="n">
-        <v>17.63458971550665</v>
+        <v>20.84628812283704</v>
       </c>
     </row>
     <row r="7">
@@ -896,31 +896,31 @@
         <v>45901</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9763894338232291</v>
+        <v>3.605695478687437</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7481919300034718</v>
+        <v>3.229153102591393</v>
       </c>
       <c r="D7" t="n">
-        <v>1.054088775196732</v>
+        <v>5.917676625087985</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7990877471336262</v>
+        <v>6.225221669164508</v>
       </c>
       <c r="F7" t="n">
-        <v>1.219284020869015</v>
+        <v>8.337392196800469</v>
       </c>
       <c r="G7" t="n">
-        <v>1.610264465700617</v>
+        <v>-0.3441808939046034</v>
       </c>
       <c r="H7" t="n">
-        <v>3.411105834148181</v>
+        <v>2.818102176995488</v>
       </c>
       <c r="I7" t="n">
-        <v>6.375266796784402</v>
+        <v>15.48018966895704</v>
       </c>
       <c r="J7" t="n">
-        <v>6.892856988083722</v>
+        <v>20.91533423218796</v>
       </c>
     </row>
   </sheetData>

--- a/Task1/drafts/results/validation_deltas.xlsx
+++ b/Task1/drafts/results/validation_deltas.xlsx
@@ -478,31 +478,31 @@
         <v>45748</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.9369229002685664</v>
+        <v>-0.5442944983977434</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.391904637841218</v>
+        <v>-0.8111510353218492</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.410119843166541</v>
+        <v>-0.9641578762020195</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.971763085761232</v>
+        <v>-1.318121966787977</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.028012516041464</v>
+        <v>-0.6029564009430786</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.505557312819249</v>
+        <v>-1.856864434986399</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.558786472824082</v>
+        <v>-2.664221069352969</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.691506127621537</v>
+        <v>-1.832849415477561</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.241090382538459</v>
+        <v>-2.481190813574827</v>
       </c>
     </row>
     <row r="3">
@@ -510,31 +510,31 @@
         <v>45778</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.662651406145372</v>
+        <v>-0.955355748152801</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.678530063224333</v>
+        <v>-1.791999088541871</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.419568661270031</v>
+        <v>-1.644338149027043</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.721388398057364</v>
+        <v>-1.782458320145317</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.046245646128526</v>
+        <v>-1.236374056351515</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.619484773353172</v>
+        <v>-1.657077797337116</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.191152319911581</v>
+        <v>-2.016500084263406</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5216008369050442</v>
+        <v>0.1883063697529579</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.414804096196335</v>
+        <v>-1.029074791113445</v>
       </c>
     </row>
     <row r="4">
@@ -542,31 +542,31 @@
         <v>45809</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.120186354614209</v>
+        <v>-0.3349914885131113</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.869028565667413</v>
+        <v>-0.9429756166004957</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.27567040234474</v>
+        <v>-0.5051947541887678</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.863641073498691</v>
+        <v>-0.8977702645302728</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.026196749163404</v>
+        <v>-0.2519833810753269</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8560390388473778</v>
+        <v>-0.03503381468166111</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.536366096099144</v>
+        <v>-1.252576333758341</v>
       </c>
       <c r="I4" t="n">
-        <v>2.168796933495486</v>
+        <v>2.511156205590183</v>
       </c>
       <c r="J4" t="n">
-        <v>3.370686534383594</v>
+        <v>3.214924080532953</v>
       </c>
     </row>
     <row r="5">
@@ -574,31 +574,31 @@
         <v>45839</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.07785047413025836</v>
+        <v>0.5683777241147219</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4991933007692921</v>
+        <v>0.2616621567687965</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09002234579124391</v>
+        <v>0.7912015482558274</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2996159236847014</v>
+        <v>1.006106739370455</v>
       </c>
       <c r="F5" t="n">
-        <v>1.381641536623896</v>
+        <v>1.950936893937836</v>
       </c>
       <c r="G5" t="n">
-        <v>2.748005311659078</v>
+        <v>3.170858246122805</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8494079767773641</v>
+        <v>1.901498200306946</v>
       </c>
       <c r="I5" t="n">
-        <v>7.285237545852375</v>
+        <v>7.10171555892088</v>
       </c>
       <c r="J5" t="n">
-        <v>8.274569290962532</v>
+        <v>7.648031968061119</v>
       </c>
     </row>
     <row r="6">
@@ -606,31 +606,31 @@
         <v>45870</v>
       </c>
       <c r="B6" t="n">
-        <v>2.818386593933177</v>
+        <v>3.115618150250395</v>
       </c>
       <c r="C6" t="n">
-        <v>2.189844031594969</v>
+        <v>2.633563359636927</v>
       </c>
       <c r="D6" t="n">
-        <v>1.837705608613255</v>
+        <v>2.356735389057771</v>
       </c>
       <c r="E6" t="n">
-        <v>3.216713496292229</v>
+        <v>3.450293262279644</v>
       </c>
       <c r="F6" t="n">
-        <v>3.476203494448992</v>
+        <v>3.740477302217119</v>
       </c>
       <c r="G6" t="n">
-        <v>6.878252835655815</v>
+        <v>6.335853824535917</v>
       </c>
       <c r="H6" t="n">
-        <v>4.049994444980804</v>
+        <v>4.723456102115009</v>
       </c>
       <c r="I6" t="n">
-        <v>12.88417111781342</v>
+        <v>11.81154558347909</v>
       </c>
       <c r="J6" t="n">
-        <v>13.31113027877863</v>
+        <v>11.83382642711506</v>
       </c>
     </row>
     <row r="7">
@@ -638,31 +638,31 @@
         <v>45901</v>
       </c>
       <c r="B7" t="n">
-        <v>4.045786251088121</v>
+        <v>4.181664076654233</v>
       </c>
       <c r="C7" t="n">
-        <v>3.167832838113675</v>
+        <v>3.449721247446401</v>
       </c>
       <c r="D7" t="n">
-        <v>3.047604372466679</v>
+        <v>3.418548571297816</v>
       </c>
       <c r="E7" t="n">
-        <v>4.583723527248889</v>
+        <v>4.629032256240745</v>
       </c>
       <c r="F7" t="n">
-        <v>4.141440107083103</v>
+        <v>4.362084486306596</v>
       </c>
       <c r="G7" t="n">
-        <v>7.656862034465981</v>
+        <v>7.025661139293959</v>
       </c>
       <c r="H7" t="n">
-        <v>4.825351393393134</v>
+        <v>5.108365594562216</v>
       </c>
       <c r="I7" t="n">
-        <v>12.65250258818565</v>
+        <v>11.5080581419769</v>
       </c>
       <c r="J7" t="n">
-        <v>13.76143448543108</v>
+        <v>12.0008741752014</v>
       </c>
     </row>
   </sheetData>
@@ -736,31 +736,31 @@
         <v>45748</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.177028621947983</v>
+        <v>-0.7123685035733338</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8930810352195202</v>
+        <v>-0.4619745134866591</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.121784985949176</v>
+        <v>-0.762323476149863</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.079773493255107</v>
+        <v>-1.393729252033687</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8562040934137372</v>
+        <v>-0.482690505103669</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.692286758484926</v>
+        <v>-2.687575046952375</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.055852571762152</v>
+        <v>-3.012167338609615</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.366615332047282</v>
+        <v>-1.605425858575579</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.320343594129156</v>
+        <v>-1.836668061688314</v>
       </c>
     </row>
     <row r="3">
@@ -768,31 +768,31 @@
         <v>45778</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.479272707501703</v>
+        <v>-0.8269906591022327</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.086766606740223</v>
+        <v>-1.377764669002996</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.20264732717003</v>
+        <v>-0.792493215157041</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.652623992562646</v>
+        <v>-1.734323236299019</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.867292785650733</v>
+        <v>-1.111107054017062</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.520659561926109</v>
+        <v>-3.687900149338176</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.751177790301291</v>
+        <v>-3.108517913536204</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7935417527163864</v>
+        <v>1.108906182487964</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9446210412678084</v>
+        <v>0.6225228051114584</v>
       </c>
     </row>
     <row r="4">
@@ -800,31 +800,31 @@
         <v>45809</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.9042156193110102</v>
+        <v>-0.1838119738008714</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.249659721445575</v>
+        <v>-0.5094174256452071</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7531078235177624</v>
+        <v>0.9149500039149814</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.064494674555903</v>
+        <v>-1.038367785270324</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3561406080231393</v>
+        <v>0.2170559177228668</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.344120169480831</v>
+        <v>-3.176690606125078</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.240133500425351</v>
+        <v>-2.445213516786687</v>
       </c>
       <c r="I4" t="n">
-        <v>3.514432344955324</v>
+        <v>3.453100993612068</v>
       </c>
       <c r="J4" t="n">
-        <v>6.286840421789321</v>
+        <v>5.256231801716964</v>
       </c>
     </row>
     <row r="5">
@@ -832,31 +832,31 @@
         <v>45839</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08224139303235489</v>
+        <v>0.6804420311285533</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1099022826946481</v>
+        <v>0.6880290651935539</v>
       </c>
       <c r="D5" t="n">
-        <v>3.064622125195196</v>
+        <v>2.873421393838594</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5214331675610993</v>
+        <v>0.4313723754983947</v>
       </c>
       <c r="F5" t="n">
-        <v>2.550280960827848</v>
+        <v>2.768984490880598</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.818250735008959</v>
+        <v>-0.7255209865448222</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7734530574600882</v>
+        <v>0.7654954763407318</v>
       </c>
       <c r="I5" t="n">
-        <v>7.805722348530104</v>
+        <v>7.466054920795294</v>
       </c>
       <c r="J5" t="n">
-        <v>12.85574076924262</v>
+        <v>10.85485200285717</v>
       </c>
     </row>
     <row r="6">
@@ -864,31 +864,31 @@
         <v>45870</v>
       </c>
       <c r="B6" t="n">
-        <v>2.327000486496317</v>
+        <v>2.771647875044593</v>
       </c>
       <c r="C6" t="n">
-        <v>2.905943674438038</v>
+        <v>3.134833109627074</v>
       </c>
       <c r="D6" t="n">
-        <v>5.142960403734612</v>
+        <v>4.670413745642719</v>
       </c>
       <c r="E6" t="n">
-        <v>3.549138537274409</v>
+        <v>3.682990790967168</v>
       </c>
       <c r="F6" t="n">
-        <v>7.30370806778399</v>
+        <v>6.419730503551616</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8847515044015992</v>
+        <v>0.9017507864957253</v>
       </c>
       <c r="H6" t="n">
-        <v>2.487640941680155</v>
+        <v>3.629808649804559</v>
       </c>
       <c r="I6" t="n">
-        <v>14.38593156287409</v>
+        <v>12.86277789502155</v>
       </c>
       <c r="J6" t="n">
-        <v>20.84628812283704</v>
+        <v>17.10843691795594</v>
       </c>
     </row>
     <row r="7">
@@ -896,31 +896,31 @@
         <v>45901</v>
       </c>
       <c r="B7" t="n">
-        <v>3.605695478687437</v>
+        <v>3.873600535973754</v>
       </c>
       <c r="C7" t="n">
-        <v>3.229153102591393</v>
+        <v>3.492645432580805</v>
       </c>
       <c r="D7" t="n">
-        <v>5.917676625087985</v>
+        <v>5.427599148132728</v>
       </c>
       <c r="E7" t="n">
-        <v>6.225221669164508</v>
+        <v>5.778080955581675</v>
       </c>
       <c r="F7" t="n">
-        <v>8.337392196800469</v>
+        <v>7.826218253680576</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3441808939046034</v>
+        <v>1.424931089434551</v>
       </c>
       <c r="H7" t="n">
-        <v>2.818102176995488</v>
+        <v>3.703291143083867</v>
       </c>
       <c r="I7" t="n">
-        <v>15.48018966895704</v>
+        <v>13.48743909851687</v>
       </c>
       <c r="J7" t="n">
-        <v>20.91533423218796</v>
+        <v>17.00860399793122</v>
       </c>
     </row>
   </sheetData>
